--- a/public/mauexcel.xlsx
+++ b/public/mauexcel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4411D12D-819F-4CE5-9B11-5EFCFA475C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254FC635-C79E-4469-B05D-44A1293C8C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,129 +15,111 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
-  <si>
-    <t>ho</t>
-  </si>
-  <si>
-    <t>ten</t>
-  </si>
-  <si>
-    <t>mota</t>
-  </si>
-  <si>
-    <t>loai</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>sodienthoai</t>
-  </si>
-  <si>
-    <t>tencongty</t>
-  </si>
-  <si>
-    <t>ngay_thanh_lap_cong_ty</t>
-  </si>
-  <si>
-    <t>diachi</t>
-  </si>
-  <si>
-    <t>trang_web</t>
-  </si>
-  <si>
-    <t>gioitinh</t>
-  </si>
-  <si>
-    <t>ngaysinh</t>
-  </si>
-  <si>
-    <t>nganh</t>
-  </si>
-  <si>
-    <t>so_giay_to</t>
-  </si>
-  <si>
-    <t>noi_cap</t>
-  </si>
-  <si>
-    <t>ngay_cap</t>
-  </si>
-  <si>
-    <t>noi_cap_giay_to</t>
-  </si>
-  <si>
-    <t>ma_so_thue</t>
-  </si>
-  <si>
-    <t>ghichu</t>
-  </si>
-  <si>
-    <t>nguoi_phu_trach</t>
-  </si>
-  <si>
-    <t>nguon_khach_hang</t>
-  </si>
-  <si>
-    <t>ngay_gia_nhap</t>
-  </si>
-  <si>
-    <t>phan_loai_khach_hang</t>
-  </si>
-  <si>
-    <t>customer@example.com</t>
-  </si>
-  <si>
-    <t>2026-01-01 00:00:00</t>
-  </si>
-  <si>
-    <t>https://example.com</t>
-  </si>
-  <si>
-    <t>male</t>
-  </si>
-  <si>
-    <t>2000-11-25 00:00:00</t>
-  </si>
-  <si>
-    <t/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+  <si>
+    <t>Họ</t>
+  </si>
+  <si>
+    <t>Tên</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>Loại khách hàng</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Tên công ty</t>
+  </si>
+  <si>
+    <t>Ngày thành lập công ty</t>
+  </si>
+  <si>
+    <t>Địa chỉ</t>
+  </si>
+  <si>
+    <t>Trang web</t>
+  </si>
+  <si>
+    <t>Giới tính</t>
+  </si>
+  <si>
+    <t>Ngày sinh</t>
+  </si>
+  <si>
+    <t>Ngành</t>
+  </si>
+  <si>
+    <t>Mã số thuế</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Nguồn khách hàng</t>
+  </si>
+  <si>
+    <t>Ngày gia nhập</t>
+  </si>
+  <si>
+    <t>Phân loại khách hàng</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Nhập mô tả về khách hàng (nếu có)</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
   </si>
   <si>
     <t>0123456789</t>
   </si>
   <si>
-    <t>my company</t>
-  </si>
-  <si>
-    <t>012345678901</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Nguyen Van</t>
-  </si>
-  <si>
-    <t>test city</t>
-  </si>
-  <si>
-    <t>test type</t>
-  </si>
-  <si>
-    <t>test description</t>
-  </si>
-  <si>
-    <t>test major</t>
-  </si>
-  <si>
-    <t>test place</t>
-  </si>
-  <si>
-    <t>test note</t>
-  </si>
-  <si>
-    <t>facebook</t>
+    <t>Nhập tên công ty của bạn</t>
+  </si>
+  <si>
+    <t>2026-04-09 00:00:00</t>
+  </si>
+  <si>
+    <t>Nhập địa chỉ của bạn</t>
+  </si>
+  <si>
+    <t>Nhập website của bạn</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>2026-04-08 00:00:00</t>
+  </si>
+  <si>
+    <t>Nhập ngành nghề của bạn</t>
+  </si>
+  <si>
+    <t>012345</t>
+  </si>
+  <si>
+    <t>Nhập ghi chú về khách hàng (nếu có)</t>
+  </si>
+  <si>
+    <t>2026-04-15 04:06:08</t>
+  </si>
+  <si>
+    <t>Nhập "Cá nhân" hoặc "Doanh nghiệp"</t>
+  </si>
+  <si>
+    <t>(nên bỏ trống)</t>
   </si>
 </sst>
 </file>
@@ -173,10 +155,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,13 +496,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="23" width="25" customWidth="1"/>
+    <col min="1" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" customWidth="1"/>
+    <col min="4" max="4" width="33.5546875" customWidth="1"/>
+    <col min="5" max="14" width="25" customWidth="1"/>
+    <col min="15" max="15" width="33.6640625" customWidth="1"/>
+    <col min="16" max="18" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -577,92 +562,65 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
       </c>
       <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="2">
-        <v>43900</v>
-      </c>
       <c r="Q2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" t="s">
-        <v>39</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>